--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487978_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487978_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6272</v>
+        <v>2.5982</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0074</v>
+        <v>3.8661</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3802</v>
+        <v>-1.2678</v>
       </c>
       <c r="G2" t="n">
         <v>0.9952</v>
@@ -610,13 +610,13 @@
         <v>0.9911</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3576</v>
+        <v>0.3285</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.4792</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.263</v>
+        <v>-0.1506</v>
       </c>
       <c r="V2" t="n">
         <v>1.2745</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>J. AGÜERA ZEA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0846</v>
+        <v>1.8107</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2398</v>
+        <v>1.8107</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1552</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6228</v>
+        <v>1.8107</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9967</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3738</v>
+        <v>1.2053</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1985</v>
+        <v>1.8107</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9938</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2048</v>
+        <v>1.2053</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5757</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9971</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5786</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4914</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0522</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4392</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.4172</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.0109</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. AGÜERA ZEA</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8107</v>
+        <v>0.9422</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8107</v>
+        <v>3.1816</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-2.2394</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8107</v>
+        <v>0.6228</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.9967</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2053</v>
+        <v>-1.3738</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8107</v>
+        <v>3.1985</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6052999999999999</v>
+        <v>2.9938</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2053</v>
+        <v>0.2048</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-2.5757</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.9971</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-1.5786</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.349</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.994</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.355</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-2.4172</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-1.0109</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.4063</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6654</v>
+        <v>0.8545</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8882</v>
+        <v>1.3581</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2228</v>
+        <v>-0.5036</v>
       </c>
       <c r="G5" t="n">
         <v>0.4915</v>
@@ -844,13 +844,13 @@
         <v>0.5947</v>
       </c>
       <c r="S5" t="n">
-        <v>0.624</v>
+        <v>0.8131</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0038</v>
+        <v>0.4737</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6202</v>
+        <v>0.3394</v>
       </c>
       <c r="V5" t="n">
         <v>0.9375</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4724</v>
+        <v>0.5286</v>
       </c>
       <c r="E6" t="n">
         <v>0.3651</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1073</v>
+        <v>0.1635</v>
       </c>
       <c r="G6" t="n">
         <v>0.6956</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2232</v>
+        <v>-0.167</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5521</v>
+        <v>-0.524</v>
       </c>
       <c r="E8" t="n">
         <v>-0.2918</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2603</v>
+        <v>-0.2322</v>
       </c>
       <c r="G8" t="n">
         <v>0.0298</v>
@@ -1078,13 +1078,13 @@
         <v>0.3964</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7118</v>
+        <v>-0.6837</v>
       </c>
       <c r="T8" t="n">
         <v>-0.312</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3998</v>
+        <v>-0.3717</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2666</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0668</v>
+        <v>-0.9473</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3956</v>
+        <v>-0.1919</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6712</v>
+        <v>-0.7554</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7911</v>
@@ -1156,13 +1156,13 @@
         <v>1.784</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.6038</v>
+        <v>-2.4843</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1855</v>
+        <v>-0.9818</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.4182</v>
+        <v>-1.5024</v>
       </c>
       <c r="V9" t="n">
         <v>1.5441</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. LASCORZ RIVARES</t>
+          <t>P. LOPEZ GOMEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1775</v>
+        <v>-2.6</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.788</v>
+        <v>-1.663</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3895</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7169</v>
+        <v>-0.8212</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5173</v>
+        <v>-3.5703</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1996</v>
+        <v>2.7492</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7294</v>
+        <v>-0.7317</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8538</v>
+        <v>-2.5073</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1244</v>
+        <v>1.7756</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9875</v>
+        <v>-0.0895</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6634</v>
+        <v>-1.0631</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3241</v>
+        <v>0.9736</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5947</v>
+        <v>1.784</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0756</v>
+        <v>-2.3558</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9325</v>
+        <v>-0.9313</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1431</v>
+        <v>-1.4244</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1397</v>
+        <v>-1.2071</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1397</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. LOPEZ GOMEZ</t>
+          <t>J. AGUERA ZEA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2426</v>
+        <v>-3.2162</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9686</v>
+        <v>1.3152</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.274</v>
+        <v>-4.5314</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8212</v>
+        <v>-2.7583</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.5703</v>
+        <v>-2.1403</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7492</v>
+        <v>-0.618</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7317</v>
+        <v>1.4163</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.5073</v>
+        <v>0.8746</v>
       </c>
       <c r="L11" t="n">
-        <v>1.7756</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0895</v>
+        <v>-4.1746</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0631</v>
+        <v>-3.0149</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9736</v>
+        <v>-1.1597</v>
       </c>
       <c r="P11" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
-        <v>1.784</v>
+        <v>2.1805</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.9983</v>
+        <v>-1.0407</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2369</v>
+        <v>-0.2467</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.7614</v>
+        <v>-0.794</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2071</v>
+        <v>-0.6066</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2071</v>
+        <v>-1.7433</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. AGUERA ZEA</t>
+          <t>F. LASCORZ RIVARES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4481</v>
+        <v>-3.3188</v>
       </c>
       <c r="E12" t="n">
-        <v>0.336</v>
+        <v>-0.9293</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.7841</v>
+        <v>-2.3895</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7583</v>
+        <v>-2.7169</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1403</v>
+        <v>-1.5173</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.618</v>
+        <v>-1.1996</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4163</v>
+        <v>-0.7294</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8746</v>
+        <v>-0.8538</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.1244</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.1746</v>
+        <v>-1.9875</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.0149</v>
+        <v>-0.6634</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1597</v>
+        <v>-1.3241</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1893</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1805</v>
+        <v>0.5947</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2726</v>
+        <v>0.9342</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2259</v>
+        <v>0.7912</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0467</v>
+        <v>0.1431</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6066</v>
+        <v>-1.1397</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7433</v>
+        <v>-1.1397</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5971</v>
+        <v>-5.2563</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3585</v>
+        <v>-2.8491</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2387</v>
+        <v>-2.4071</v>
       </c>
       <c r="G13" t="n">
         <v>-0.25</v>
@@ -1468,13 +1468,13 @@
         <v>1.9822</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.4948</v>
+        <v>-2.1539</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2369</v>
+        <v>-0.7276</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2579</v>
+        <v>-1.4263</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8701</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.9254</v>
+        <v>-9.908799999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.2323</v>
+        <v>-8.0472</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6931</v>
+        <v>-1.8616</v>
       </c>
       <c r="G14" t="n">
         <v>-3.9565</v>
@@ -1546,13 +1546,13 @@
         <v>2.1805</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9162</v>
+        <v>-1.8997</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2461</v>
+        <v>-0.5688</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1624</v>
+        <v>-1.3309</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2775</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-19.0466</v>
+        <v>-18.7345</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.084900000000001</v>
+        <v>-1.772799999999998</v>
       </c>
       <c r="F15" t="n">
-        <v>-16.9618</v>
+        <v>-16.9615</v>
       </c>
       <c r="G15" t="n">
         <v>-7.345700000000001</v>
@@ -1600,7 +1600,7 @@
         <v>9.384799999999998</v>
       </c>
       <c r="K15" t="n">
-        <v>3.529299999999999</v>
+        <v>3.5293</v>
       </c>
       <c r="L15" t="n">
         <v>5.855700000000001</v>
@@ -1624,13 +1624,13 @@
         <v>13.8757</v>
       </c>
       <c r="S15" t="n">
-        <v>-7.6721</v>
+        <v>-7.3603</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4669</v>
+        <v>-1.1549</v>
       </c>
       <c r="U15" t="n">
-        <v>-6.205299999999999</v>
+        <v>-6.205</v>
       </c>
       <c r="V15" t="n">
         <v>-4.0287</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.2075</v>
+        <v>8.2173</v>
       </c>
       <c r="E16" t="n">
-        <v>7.795</v>
+        <v>8.202500000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4125</v>
+        <v>0.0149</v>
       </c>
       <c r="G16" t="n">
         <v>4.5116</v>
@@ -1702,13 +1702,13 @@
         <v>1.5858</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4738</v>
+        <v>0.4836</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3706</v>
+        <v>0.0369</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8444</v>
+        <v>0.4467</v>
       </c>
       <c r="V16" t="n">
         <v>2.6275</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.519</v>
+        <v>6.0165</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0414</v>
+        <v>4.347</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4776</v>
+        <v>1.6696</v>
       </c>
       <c r="G17" t="n">
         <v>5.0145</v>
@@ -1780,13 +1780,13 @@
         <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0984</v>
+        <v>0.3992</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0072</v>
+        <v>0.2984</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0911</v>
+        <v>0.1008</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5865</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.2847</v>
+        <v>5.7117</v>
       </c>
       <c r="E18" t="n">
-        <v>6.4727</v>
+        <v>6.3708</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.188</v>
+        <v>-0.659</v>
       </c>
       <c r="G18" t="n">
         <v>2.3491</v>
@@ -1858,13 +1858,13 @@
         <v>1.784</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4531</v>
+        <v>0.8801</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9253</v>
+        <v>0.8234</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4722</v>
+        <v>0.0567</v>
       </c>
       <c r="V18" t="n">
         <v>2.6808</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.7361</v>
+        <v>2.9375</v>
       </c>
       <c r="E19" t="n">
-        <v>4.619</v>
+        <v>3.6003</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8829</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0.7681</v>
@@ -1936,13 +1936,13 @@
         <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7103</v>
+        <v>1.9116</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5331</v>
+        <v>1.5144</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1772</v>
+        <v>0.3972</v>
       </c>
       <c r="V19" t="n">
         <v>-0.337</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8138</v>
+        <v>2.6229</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1855</v>
+        <v>-0.6762</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9993</v>
+        <v>3.2991</v>
       </c>
       <c r="G20" t="n">
         <v>3.275</v>
@@ -2014,13 +2014,13 @@
         <v>2.3787</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3484</v>
+        <v>0.4607</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6312</v>
+        <v>-0.1219</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2828</v>
+        <v>0.5825</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3199</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4996</v>
+        <v>0.8849</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7534</v>
+        <v>1.059</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2538</v>
+        <v>-0.1742</v>
       </c>
       <c r="G21" t="n">
         <v>-2.7414</v>
@@ -2092,13 +2092,13 @@
         <v>1.1893</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0161</v>
+        <v>1.4014</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.9261</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3956</v>
+        <v>0.4752</v>
       </c>
       <c r="V21" t="n">
         <v>3.0178</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS LAJARA</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2185</v>
+        <v>0.0322</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0243</v>
+        <v>-0.2175</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2429</v>
+        <v>0.2497</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0615</v>
+        <v>0.2198</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0748</v>
+        <v>1.7082</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1364</v>
+        <v>-1.4884</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3428</v>
+        <v>0.2761</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9351</v>
+        <v>1.6344</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2779</v>
+        <v>-1.3583</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2813</v>
+        <v>-0.0563</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1398</v>
+        <v>0.0738</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1415</v>
+        <v>-0.1301</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3964</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R22" t="n">
         <v>0.3964</v>
       </c>
       <c r="S22" t="n">
-        <v>0.707</v>
+        <v>0.6736</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3671</v>
+        <v>0.4975</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3398</v>
+        <v>0.1762</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2604</v>
+        <v>-0.2666</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2604</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MARTOS BONACHELA</t>
+          <t>R. REQUENA ESCABIAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5044</v>
+        <v>-0.3645</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.659</v>
+        <v>-0.1977</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1545</v>
+        <v>-0.1668</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5231</v>
+        <v>-0.1357</v>
       </c>
       <c r="H23" t="n">
-        <v>0.156</v>
+        <v>-0.0458</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6791</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.659</v>
+        <v>0.0604</v>
       </c>
       <c r="K23" t="n">
         <v>0.0202</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6791</v>
+        <v>0.0402</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1358</v>
+        <v>-0.1961</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1358</v>
+        <v>-0.066</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-0.1301</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2248,28 +2248,28 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0187</v>
+        <v>0.1615</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>0.0789</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0187</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.3903</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.0533</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. REQUENA ESCABIAS</t>
+          <t>A. MARTOS BONACHELA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,40 +2281,40 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5121</v>
+        <v>-0.3745</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4014</v>
+        <v>-0.5571</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1107</v>
+        <v>0.1826</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1357</v>
+        <v>-0.5231</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0458</v>
+        <v>0.156</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.6791</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0604</v>
+        <v>-0.659</v>
       </c>
       <c r="K24" t="n">
         <v>0.0202</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0402</v>
+        <v>-0.6791</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1961</v>
+        <v>0.1358</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.066</v>
+        <v>0.1358</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1301</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2326,28 +2326,28 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0139</v>
+        <v>0.1487</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1248</v>
+        <v>0.1019</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1387</v>
+        <v>0.0468</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3903</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>S. TORRECILLAS LAJARA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7149</v>
+        <v>-0.4327</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8287</v>
+        <v>-0.0775</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1139</v>
+        <v>-0.3552</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2198</v>
+        <v>-0.0615</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7082</v>
+        <v>1.0748</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4884</v>
+        <v>-1.1364</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2761</v>
+        <v>-0.3428</v>
       </c>
       <c r="K25" t="n">
-        <v>1.6344</v>
+        <v>0.9351</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3583</v>
+        <v>-1.2779</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0563</v>
+        <v>0.2813</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0738</v>
+        <v>0.1398</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1301</v>
+        <v>0.1415</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0.3964</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.07340000000000001</v>
+        <v>0.4928</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1138</v>
+        <v>0.2653</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0403</v>
+        <v>0.2275</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.2666</v>
+        <v>-1.2604</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.2666</v>
+        <v>-1.2604</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.9828</v>
+        <v>-2.1317</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.523</v>
+        <v>-2.0324</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4598</v>
+        <v>-0.0993</v>
       </c>
       <c r="G26" t="n">
         <v>-2.0562</v>
@@ -2482,13 +2482,13 @@
         <v>1.1893</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2805</v>
+        <v>1.1316</v>
       </c>
       <c r="T26" t="n">
-        <v>1.5382</v>
+        <v>1.0289</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2577</v>
+        <v>0.1027</v>
       </c>
       <c r="V26" t="n">
         <v>-1.2071</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.0814</v>
+        <v>-2.7148</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.1464</v>
+        <v>-2.8595</v>
       </c>
       <c r="F27" t="n">
-        <v>0.065</v>
+        <v>0.1447</v>
       </c>
       <c r="G27" t="n">
         <v>-3.2744</v>
@@ -2560,13 +2560,13 @@
         <v>1.784</v>
       </c>
       <c r="S27" t="n">
-        <v>1.519</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>1.4686</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0505</v>
+        <v>0.1301</v>
       </c>
       <c r="V27" t="n">
         <v>0.0704</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>19.0466</v>
+        <v>20.4048</v>
       </c>
       <c r="E28" t="n">
-        <v>16.9618</v>
+        <v>16.9617</v>
       </c>
       <c r="F28" t="n">
-        <v>2.0847</v>
+        <v>3.4433</v>
       </c>
       <c r="G28" t="n">
         <v>7.345799999999999</v>
@@ -2620,16 +2620,16 @@
         <v>2.374500000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>-9.384700000000002</v>
+        <v>-9.3847</v>
       </c>
       <c r="N28" t="n">
         <v>-3.529199999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>-5.855599999999999</v>
+        <v>-5.8556</v>
       </c>
       <c r="P28" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="Q28" t="n">
         <v>-13.8755</v>
@@ -2638,13 +2638,13 @@
         <v>13.8755</v>
       </c>
       <c r="S28" t="n">
-        <v>7.672199999999999</v>
+        <v>9.0304</v>
       </c>
       <c r="T28" t="n">
-        <v>6.2052</v>
+        <v>6.205299999999999</v>
       </c>
       <c r="U28" t="n">
-        <v>1.467</v>
+        <v>2.825</v>
       </c>
       <c r="V28" t="n">
         <v>4.0287</v>
